--- a/deliverables/CSPro/supervisor-hub/assignments/assignment-master.xlsx
+++ b/deliverables/CSPro/supervisor-hub/assignments/assignment-master.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="hidden" r:id="rId1"/>
-    <sheet name="Assignments" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Enumerators" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignments" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enumerators" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -551,275 +551,296 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Pre-loaded with the Round 6 assignments (Laguna pretest). Edit / add rows for later rounds.</t>
+          <t>Pre-loaded with the Los Baños pre-test assignments (RA 'Unique Question Number' list,</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>municipality 040341). R6 roster names reused. Edit / add rows for later rounds.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>What this is</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>One row per (enumerator x EA/facility). It carries exactly what the hub's assignment</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>record needs. Fill the Assignments sheet, then run generate_assignments.py to produce:</t>
+          <t>One row per (enumerator x EA/facility). It carries exactly what the hub's assignment</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   •  AS_&lt;enumerator_id&gt;.dat  — the per-enumerator file the hub's 'Assign Enumeration</t>
+          <t>record needs. Fill the Assignments sheet, then run generate_assignments.py to produce:</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Area' serves over Bluetooth (enumerator pulls it via 'Receive Assigned Data').</t>
+          <t xml:space="preserve">   •  AS_&lt;enumerator_id&gt;.dat  — the per-enumerator file the hub's 'Assign Enumeration</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   •  assignment-sheets.html — printable case-key sheets (the reliable hand-out path).</t>
+          <t xml:space="preserve">      Area' serves over Bluetooth (enumerator pulls it via 'Receive Assigned Data').</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   •  assignment-sheets.html — printable case-key sheets (the reliable hand-out path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   •  case-keys.csv          — every 12-digit case key, for QA / CSWeb cross-check.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>You assign AREAS + TARGETS, not individual respondents</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>The unit is the EA / facility, with a target case count — NOT a named respondent.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>F1 = one facility head per facility · F3 = patients recruited on-site up to target ·</t>
+          <t>The unit is the EA / facility, with a target case count — NOT a named respondent.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>F4 = households up to target (members are rostered inside the interview). Respondent /</t>
+          <t>F1 = one facility head per facility · F3 = patients recruited on-site up to target ·</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>F4 = households up to target (members are rostered inside the interview). Respondent /</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>household pre-listing is descoped from hub v1, so nobody is assigned by name.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>The case key</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>12 digits = the 9-digit EA/facility code (real PSGC) + a 3-digit sequence (001..target).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>e.g. EA 040340002, target 12  -&gt;  040340002001 ... 040340002012.</t>
+          <t>12 digits = the 9-digit EA/facility code (real PSGC) + a 3-digit sequence.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>A wrong PSGC prefix is hard-rejected on the tablet, so use REAL codes only.</t>
+          <t>When first/last_case_key are filled (as here, from the RA QN list) they are AUTHORITATIVE —</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>the generator emits those exact keys verbatim (the RA numbering isn't always 001-based:</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Columns to fill (Assignments sheet)</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>facility-head keys end 000, and Brgy. Bayog runs 601..620). Leave first/last blank and the</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   supervisor_id    the enumerator's supervisor (fs-01 / fs-02). Review-only — shows the chain.</t>
+          <t>generator falls back to code + 001..target. A wrong PSGC prefix is hard-rejected on the tablet.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   enumerator_id    login of the enumerator (e.g. se-001). Names the .dat file + the row.</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   enumerator_name  label only (for the printed sheet); not sent to the tablet.</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Columns to fill (Assignments sheet)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   facility_code    9-digit EA/facility code, real PSGC (RRPPMMMFF).</t>
+          <t xml:space="preserve">   supervisor_id    the enumerator's supervisor (fs-01 / fs-02). Review-only — shows the chain.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   instrument       F1, F3, or F4.</t>
+          <t xml:space="preserve">   enumerator_id    login of the enumerator (e.g. se-001). Names the .dat file + the row.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   target_count     how many cases to complete at that EA.</t>
+          <t xml:space="preserve">   enumerator_name  label only (for the printed sheet); not sent to the tablet.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ea_name          EA / facility name (label).</t>
+          <t xml:space="preserve">   facility_code    9-digit EA/facility code, real PSGC (RRPPMMMFF).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   cluster          cluster label (free text).</t>
+          <t xml:space="preserve">   instrument       F1, F3, or F4.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   first/last key   AUTO — shows the case-key range so you can eyeball it. Don't edit.</t>
+          <t xml:space="preserve">   target_count     how many cases to complete at that EA.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   RA confirmed?    REVIEWER fills — 'OK' per verified row, or 'needs fix'.</t>
+          <t xml:space="preserve">   ea_name          EA / facility name (label).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   RA notes         REVIEWER fills — corrections (real facility code, target, name…).</t>
+          <t xml:space="preserve">   cluster          cluster label (free text).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr"/>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   first/last key   the exact 12-digit QN range from the RA list. Authoritative — emitted verbatim.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Two distribution paths (field-protocol choice)</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   RA confirmed?    REVIEWER fills — 'OK' per verified row, or 'needs fix'.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1.  Assignment sheet  — print assignment-sheets.html; enumerator TYPES the 12-digit</t>
+          <t xml:space="preserve">   RA notes         REVIEWER fills — corrections (real facility code, target, name…).</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       keys. Needs no pairing; the PSGC gate protects key integrity. RELIABLE TODAY.</t>
-        </is>
-      </c>
+      <c r="A39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   2.  Hub Bluetooth     — 'Assign Enumeration Area' serves AS_&lt;id&gt;.dat; enumerator runs</t>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Two distribution paths (field-protocol choice)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">       'Receive Assigned Data'. Nicer, no internet — but DEVICE-VERIFY PENDING (the</t>
+          <t xml:space="preserve">   1.  Assignment sheet  — print assignment-sheets.html; enumerator TYPES the 12-digit</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">       syncfile-over-Bluetooth leg hasn't been run on the 2-tablet rig yet).</t>
+          <t xml:space="preserve">       keys. Needs no pairing; the PSGC gate protects key integrity. RELIABLE TODAY.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr"/>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2.  Hub Bluetooth     — 'Assign Enumeration Area' serves AS_&lt;id&gt;.dat; enumerator runs</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Recommendation: use the printed sheet for the pretest; switch to Bluetooth once the</t>
+          <t xml:space="preserve">       'Receive Assigned Data'. Nicer, no internet — but DEVICE-VERIFY PENDING (the</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       syncfile-over-Bluetooth leg hasn't been run on the 2-tablet rig yet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Recommendation: use the printed sheet for the pretest; switch to Bluetooth once the</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Assign/Receive leg is device-verified.</t>
         </is>
@@ -836,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -933,7 +954,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>040340001</t>
+          <t>040341110</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -946,21 +967,23 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>Binan City Health Office</t>
+          <t>Los Banos Doctors Hospital - Facility Head</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>04034</t>
-        </is>
-      </c>
-      <c r="I2" s="10">
-        <f>D2&amp;"001"</f>
-        <v/>
-      </c>
-      <c r="J2" s="10">
-        <f>D2&amp;TEXT(F2,"000")</f>
-        <v/>
+          <t>040341</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>040341110000</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>040341110000</t>
+        </is>
       </c>
       <c r="K2" s="11" t="n"/>
       <c r="L2" s="12" t="n"/>
@@ -973,17 +996,17 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>se-002</t>
+          <t>se-001</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Shan</t>
+          <t>Pat</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>040340002</t>
+          <t>040341110</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -992,25 +1015,27 @@
         </is>
       </c>
       <c r="F3" s="9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Binan RHU - Patient Survey</t>
+          <t>Los Banos Doctors Hospital - Patient</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>04034</t>
-        </is>
-      </c>
-      <c r="I3" s="10">
-        <f>D3&amp;"001"</f>
-        <v/>
-      </c>
-      <c r="J3" s="10">
-        <f>D3&amp;TEXT(F3,"000")</f>
-        <v/>
+          <t>040341</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>040341110001</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>040341110010</t>
+        </is>
       </c>
       <c r="K3" s="11" t="n"/>
       <c r="L3" s="12" t="n"/>
@@ -1023,44 +1048,46 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>se-003</t>
+          <t>se-002</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Aly</t>
+          <t>Shan</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>040340005</t>
+          <t>040341120</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Binan Brgy Malaban - Household Survey</t>
+          <t>Laguna Provincial Hospital Bay - Facility Head</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>04034</t>
-        </is>
-      </c>
-      <c r="I4" s="10">
-        <f>D4&amp;"001"</f>
-        <v/>
-      </c>
-      <c r="J4" s="10">
-        <f>D4&amp;TEXT(F4,"000")</f>
-        <v/>
+          <t>040341</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>040341120000</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>040341120000</t>
+        </is>
       </c>
       <c r="K4" s="11" t="n"/>
       <c r="L4" s="12" t="n"/>
@@ -1073,44 +1100,46 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>se-004</t>
+          <t>se-002</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Marriz</t>
+          <t>Shan</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>040340011</t>
+          <t>040341120</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Binan District Hospital - Facility Head</t>
+          <t>Laguna Provincial Hospital Bay - Patient</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>04034</t>
-        </is>
-      </c>
-      <c r="I5" s="10">
-        <f>D5&amp;"001"</f>
-        <v/>
-      </c>
-      <c r="J5" s="10">
-        <f>D5&amp;TEXT(F5,"000")</f>
-        <v/>
+          <t>040341</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>040341120001</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>040341120010</t>
+        </is>
       </c>
       <c r="K5" s="11" t="n"/>
       <c r="L5" s="12" t="n"/>
@@ -1118,49 +1147,51 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>fs-02</t>
+          <t>fs-01</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>se-005</t>
+          <t>se-004</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Aidan</t>
+          <t>Marriz</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>040341002</t>
+          <t>040341130</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Los Banos RHU - Patient Survey</t>
+          <t>Los Banos RHU I - Facility Head</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>04034</t>
-        </is>
-      </c>
-      <c r="I6" s="10">
-        <f>D6&amp;"001"</f>
-        <v/>
-      </c>
-      <c r="J6" s="10">
-        <f>D6&amp;TEXT(F6,"000")</f>
-        <v/>
+          <t>040341</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>040341130000</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>040341130000</t>
+        </is>
       </c>
       <c r="K6" s="11" t="n"/>
       <c r="L6" s="12" t="n"/>
@@ -1168,63 +1199,273 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>fs-02</t>
+          <t>fs-01</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>se-006</t>
+          <t>se-004</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Merlyne</t>
+          <t>Marriz</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>040341005</t>
+          <t>040341130</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="F7" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Los Banos Brgy Mayondon - Household Survey</t>
+          <t>Los Banos RHU I - Patient</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>04034</t>
-        </is>
-      </c>
-      <c r="I7" s="10">
-        <f>D7&amp;"001"</f>
-        <v/>
-      </c>
-      <c r="J7" s="10">
-        <f>D7&amp;TEXT(F7,"000")</f>
-        <v/>
+          <t>040341</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>040341130001</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>040341130010</t>
+        </is>
       </c>
       <c r="K7" s="11" t="n"/>
       <c r="L7" s="12" t="n"/>
     </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>fs-01</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>se-003</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Aly</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>040341100</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Brgy. Bayog - Household</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>040341</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>040341100601</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>040341100620</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="12" t="n"/>
+    </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>↑ Round-6 assignments (Laguna pretest: Biñan = Team A · Los Baños = Team B). Blue = you fill · grey = auto. Edit / add rows for later rounds.</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>fs-02</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>se-005</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Aidan</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>040341140</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>St. Jude Hospital - Facility Head</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>040341</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>040341140000</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>040341140000</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>fs-02</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>se-005</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Aidan</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>040341140</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>St. Jude Hospital - Patient</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>040341</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>040341140001</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>040341140010</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="12" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>fs-02</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>se-006</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Merlyne</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>040341101</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Brgy. Mayondon - Household</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>040341</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>040341101001</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>040341101020</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>↑ Los Baños pre-test (RA QN list, municipality 040341; R6 roster names). 4 facilities = F1 head + F3 patients · 2 barangays = F4. Blue = you fill · grey = QN range from the RA list (verbatim). Edit / add rows for later rounds.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A13:L13"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Choose F1, F3, or F4" prompt="F1 = Facility Head · F3 = Patient · F4 = Household" type="list">

--- a/deliverables/CSPro/supervisor-hub/assignments/assignment-master.xlsx
+++ b/deliverables/CSPro/supervisor-hub/assignments/assignment-master.xlsx
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Merlyne</t>
+          <t>Aly</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
